--- a/KatalonData/RADTestData/MFLNNotZero.xlsx
+++ b/KatalonData/RADTestData/MFLNNotZero.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{E79BB77B-80A9-43F5-8B7D-A5F603629FDE}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77942AB-B51F-4C71-8CE1-2AD5EED8BB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-98"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
-    <sheet name="MFLNNotZero" r:id="rId1" sheetId="4"/>
+    <sheet name="MFLNNotZero" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">MFLNNotZero!$E$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MFLNNotZero!$E$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>Result</t>
   </si>
@@ -71,22 +71,22 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Sat Jun 20 22:54:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 20 22:54:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Defect, No Error for being Zero</t>
-  </si>
-  <si>
-    <t>Sat Jun 20 23:01:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Sat Jun 20 23:02:10 EDT 2026</t>
+    <t>Thu Jun 25 14:48:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 14:48:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:57:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:57:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:02:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:02:23 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -142,19 +142,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -171,10 +171,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -209,7 +209,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -261,7 +261,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -372,21 +372,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -403,7 +403,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -455,15 +455,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -475,7 +475,7 @@
     <col min="7" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,12 +492,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -509,11 +509,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -524,15 +524,12 @@
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="E1:E2" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
